--- a/fee_data_complete_base_20260602_summary.xlsx
+++ b/fee_data_complete_base_20260602_summary.xlsx
@@ -866,7 +866,7 @@
         <v>164</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5452.18</v>
+        <v>5437.34</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>5452.18</v>
@@ -878,7 +878,7 @@
         <v>155</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>5311.07</v>
+        <v>5296.5</v>
       </c>
       <c r="I4" s="10" t="n">
         <v>5311.07</v>
@@ -890,7 +890,7 @@
         <v>151</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>4851.11</v>
+        <v>4837.77</v>
       </c>
       <c r="M4" s="10" t="n">
         <v>4851.11</v>
@@ -902,7 +902,7 @@
         <v>470</v>
       </c>
       <c r="P4" s="10" t="n">
-        <v>15614.35</v>
+        <v>15571.61</v>
       </c>
       <c r="Q4" s="10" t="n">
         <v>15614.35</v>
@@ -1012,7 +1012,7 @@
         <v>168</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>4374.01</v>
+        <v>4294.6</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>4374.01</v>
@@ -1024,7 +1024,7 @@
         <v>164</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>4407.79</v>
+        <v>4327.61</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>4407.79</v>
@@ -1036,7 +1036,7 @@
         <v>157</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>4157.72</v>
+        <v>4081.83</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>4157.72</v>
@@ -1048,7 +1048,7 @@
         <v>489</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>12939.51</v>
+        <v>12704.04</v>
       </c>
       <c r="Q6" s="10" t="n">
         <v>12939.51</v>
@@ -1454,7 +1454,7 @@
         <v>101</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>2230.68</v>
+        <v>2217.06</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>1115.34</v>
@@ -1466,7 +1466,7 @@
         <v>104</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>2443.46</v>
+        <v>2433.41</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>1221.73</v>
@@ -1478,7 +1478,7 @@
         <v>106</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>2409.3</v>
+        <v>2399.01</v>
       </c>
       <c r="M12" s="10" t="n">
         <v>1204.65</v>
@@ -1490,7 +1490,7 @@
         <v>311</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>7083.43</v>
+        <v>7049.49</v>
       </c>
       <c r="Q12" s="10" t="n">
         <v>3541.72</v>
@@ -1608,7 +1608,7 @@
         <v>141</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3904.62</v>
+        <v>2004.56</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>1005.86</v>
@@ -1620,7 +1620,7 @@
         <v>139</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>4187.91</v>
+        <v>2150.99</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>1079.37</v>
@@ -1632,7 +1632,7 @@
         <v>139</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>4375.81</v>
+        <v>2222.89</v>
       </c>
       <c r="M14" s="10" t="n">
         <v>1115.53</v>
@@ -1644,7 +1644,7 @@
         <v>419</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>12468.35</v>
+        <v>6378.44</v>
       </c>
       <c r="Q14" s="10" t="n">
         <v>3200.77</v>
@@ -1770,7 +1770,7 @@
         <v>75</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>2568.82</v>
+        <v>1730.61</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>642.39</v>
@@ -1782,7 +1782,7 @@
         <v>74</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>2675.34</v>
+        <v>1779.7</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>652.1</v>
@@ -1794,7 +1794,7 @@
         <v>74</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>2678.37</v>
+        <v>1786.84</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>657.5700000000001</v>
@@ -1806,7 +1806,7 @@
         <v>223</v>
       </c>
       <c r="P16" s="10" t="n">
-        <v>7922.53</v>
+        <v>5297.15</v>
       </c>
       <c r="Q16" s="10" t="n">
         <v>1952.07</v>
@@ -1849,7 +1849,7 @@
         <v>39</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>1821.57</v>
+        <v>1806.74</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>1791.9</v>
@@ -1861,7 +1861,7 @@
         <v>38</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1642.45</v>
+        <v>1627.88</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>1613.32</v>
@@ -1873,7 +1873,7 @@
         <v>42</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>1584.25</v>
+        <v>1570.91</v>
       </c>
       <c r="M17" s="8" t="n">
         <v>1557.57</v>
@@ -1885,7 +1885,7 @@
         <v>119</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>5048.28</v>
+        <v>5005.54</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>4962.8</v>
@@ -1922,7 +1922,7 @@
         <v>68</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2486.8</v>
+        <v>1296.1</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>1243.4</v>
@@ -1934,7 +1934,7 @@
         <v>68</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>2707.04</v>
+        <v>1412.96</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>1353.52</v>
@@ -1946,7 +1946,7 @@
         <v>68</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>2737.74</v>
+        <v>1432.39</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>1368.87</v>
@@ -1958,7 +1958,7 @@
         <v>204</v>
       </c>
       <c r="P18" s="10" t="n">
-        <v>7931.57</v>
+        <v>4141.45</v>
       </c>
       <c r="Q18" s="10" t="n">
         <v>3965.79</v>
@@ -2074,7 +2074,7 @@
         <v>184</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2570.68</v>
+        <v>1294.1</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>650.8099999999999</v>
@@ -2086,7 +2086,7 @@
         <v>183</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>2812.58</v>
+        <v>1416.02</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>712.1799999999999</v>
@@ -2098,7 +2098,7 @@
         <v>179</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>1808.07</v>
+        <v>914.48</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>462.2</v>
@@ -2110,7 +2110,7 @@
         <v>546</v>
       </c>
       <c r="P20" s="10" t="n">
-        <v>7191.33</v>
+        <v>3624.59</v>
       </c>
       <c r="Q20" s="10" t="n">
         <v>1825.2</v>
@@ -2157,7 +2157,7 @@
         <v>60</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1086.48</v>
+        <v>1047.93</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>532.4299999999999</v>
@@ -2169,7 +2169,7 @@
         <v>58</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1156.38</v>
+        <v>1125.61</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>568.61</v>
@@ -2181,7 +2181,7 @@
         <v>54</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>1055.11</v>
+        <v>1044.77</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>517.22</v>
@@ -2193,7 +2193,7 @@
         <v>172</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>3297.97</v>
+        <v>3218.31</v>
       </c>
       <c r="Q21" s="8" t="n">
         <v>1618.26</v>
@@ -2236,7 +2236,7 @@
         <v>42</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>1014.77</v>
+        <v>999.78</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>830.39</v>
@@ -2248,7 +2248,7 @@
         <v>42</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>1077.92</v>
+        <v>1062.33</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>817.04</v>
@@ -2260,7 +2260,7 @@
         <v>43</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>1031.52</v>
+        <v>1018.84</v>
       </c>
       <c r="M22" s="10" t="n">
         <v>800.14</v>
@@ -2272,7 +2272,7 @@
         <v>127</v>
       </c>
       <c r="P22" s="10" t="n">
-        <v>3124.21</v>
+        <v>3080.95</v>
       </c>
       <c r="Q22" s="10" t="n">
         <v>2447.58</v>
@@ -2473,7 +2473,7 @@
         <v>33</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>1035.44</v>
+        <v>953.58</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>876.63</v>
@@ -2485,7 +2485,7 @@
         <v>38</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1056.94</v>
+        <v>974.66</v>
       </c>
       <c r="I25" s="8" t="n">
         <v>896.58</v>
@@ -2497,7 +2497,7 @@
         <v>43</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>1024.04</v>
+        <v>946.5700000000001</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>872.27</v>
@@ -2509,7 +2509,7 @@
         <v>114</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>3116.41</v>
+        <v>2874.81</v>
       </c>
       <c r="Q25" s="8" t="n">
         <v>2645.48</v>
@@ -2548,7 +2548,7 @@
         <v>58</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2029.76</v>
+        <v>884.98</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>76.06</v>
@@ -2560,7 +2560,7 @@
         <v>58</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>2218.52</v>
+        <v>973.58</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>86.01000000000001</v>
@@ -2572,7 +2572,7 @@
         <v>58</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>2249.83</v>
+        <v>994.78</v>
       </c>
       <c r="M26" s="10" t="n">
         <v>92.55</v>
@@ -2584,7 +2584,7 @@
         <v>174</v>
       </c>
       <c r="P26" s="10" t="n">
-        <v>6498.11</v>
+        <v>2853.34</v>
       </c>
       <c r="Q26" s="10" t="n">
         <v>254.63</v>
@@ -2704,7 +2704,7 @@
         <v>47</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1235.13</v>
+        <v>885.9299999999999</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>380.5</v>
@@ -2716,7 +2716,7 @@
         <v>46</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>1321.91</v>
+        <v>951.85</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>409.22</v>
@@ -2728,7 +2728,7 @@
         <v>42</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>1301.98</v>
+        <v>926.29</v>
       </c>
       <c r="M28" s="10" t="n">
         <v>395.05</v>
@@ -2740,7 +2740,7 @@
         <v>135</v>
       </c>
       <c r="P28" s="10" t="n">
-        <v>3859.02</v>
+        <v>2764.08</v>
       </c>
       <c r="Q28" s="10" t="n">
         <v>1184.76</v>
@@ -3016,7 +3016,7 @@
         <v>64</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>758.09</v>
+        <v>744.6900000000001</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>365.65</v>
@@ -3028,7 +3028,7 @@
         <v>63</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>855.96</v>
+        <v>841.03</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>413.05</v>
@@ -3040,7 +3040,7 @@
         <v>60</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>838.28</v>
+        <v>825.33</v>
       </c>
       <c r="M32" s="10" t="n">
         <v>406.19</v>
@@ -3052,7 +3052,7 @@
         <v>187</v>
       </c>
       <c r="P32" s="10" t="n">
-        <v>2452.34</v>
+        <v>2411.05</v>
       </c>
       <c r="Q32" s="10" t="n">
         <v>1184.89</v>
@@ -3168,7 +3168,7 @@
         <v>84</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>777.6</v>
+        <v>766.67</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>377.87</v>
@@ -3180,7 +3180,7 @@
         <v>85</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>859.1900000000001</v>
+        <v>847.23</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>417.63</v>
@@ -3204,7 +3204,7 @@
         <v>250</v>
       </c>
       <c r="P34" s="10" t="n">
-        <v>2199.77</v>
+        <v>2176.88</v>
       </c>
       <c r="Q34" s="10" t="n">
         <v>1076.99</v>
@@ -3399,7 +3399,7 @@
         <v>45</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>613.97</v>
+        <v>605.89</v>
       </c>
       <c r="E37" s="8" t="n">
         <v>306.99</v>
@@ -3411,7 +3411,7 @@
         <v>46</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>708.89</v>
+        <v>699.59</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>354.44</v>
@@ -3423,7 +3423,7 @@
         <v>48</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>805.64</v>
+        <v>797.03</v>
       </c>
       <c r="M37" s="8" t="n">
         <v>402.82</v>
@@ -3435,7 +3435,7 @@
         <v>139</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>2128.5</v>
+        <v>2102.52</v>
       </c>
       <c r="Q37" s="8" t="n">
         <v>1064.25</v>
@@ -3478,7 +3478,7 @@
         <v>19</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>671.79</v>
+        <v>581.67</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>245.78</v>
@@ -3490,7 +3490,7 @@
         <v>19</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>733.05</v>
+        <v>635.26</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>268.73</v>
@@ -3502,7 +3502,7 @@
         <v>19</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>764.54</v>
+        <v>662</v>
       </c>
       <c r="M38" s="10" t="n">
         <v>279.73</v>
@@ -3514,7 +3514,7 @@
         <v>57</v>
       </c>
       <c r="P38" s="10" t="n">
-        <v>2169.39</v>
+        <v>1878.93</v>
       </c>
       <c r="Q38" s="10" t="n">
         <v>794.24</v>
@@ -3557,7 +3557,7 @@
         <v>31</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>743.45</v>
+        <v>654.1799999999999</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>729.09</v>
@@ -3569,7 +3569,7 @@
         <v>31</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>748.25</v>
+        <v>661.9</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>734.4299999999999</v>
@@ -3581,7 +3581,7 @@
         <v>29</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>634.04</v>
+        <v>554.37</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>621.66</v>
@@ -3593,7 +3593,7 @@
         <v>91</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>2125.75</v>
+        <v>1870.45</v>
       </c>
       <c r="Q39" s="8" t="n">
         <v>2085.18</v>
@@ -3786,7 +3786,7 @@
         <v>33</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>688.4299999999999</v>
+        <v>568.9400000000001</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>688.4299999999999</v>
@@ -3798,7 +3798,7 @@
         <v>35</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>751.29</v>
+        <v>627.4</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>751.29</v>
@@ -3810,7 +3810,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>755.4299999999999</v>
+        <v>635.34</v>
       </c>
       <c r="M42" s="10" t="n">
         <v>755.4299999999999</v>
@@ -3822,7 +3822,7 @@
         <v>105</v>
       </c>
       <c r="P42" s="10" t="n">
-        <v>2195.15</v>
+        <v>1831.68</v>
       </c>
       <c r="Q42" s="10" t="n">
         <v>2195.15</v>
@@ -4017,7 +4017,7 @@
         <v>22</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>590.35</v>
+        <v>589.89</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>589.42</v>
@@ -4029,7 +4029,7 @@
         <v>20</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>552.12</v>
+        <v>550.9299999999999</v>
       </c>
       <c r="I45" s="8" t="n">
         <v>549.74</v>
@@ -4041,7 +4041,7 @@
         <v>20</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>523.13</v>
+        <v>522.25</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>521.37</v>
@@ -4053,7 +4053,7 @@
         <v>62</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>1665.6</v>
+        <v>1663.07</v>
       </c>
       <c r="Q45" s="8" t="n">
         <v>1660.53</v>
@@ -4163,7 +4163,7 @@
         <v>23</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>596.99</v>
+        <v>558.51</v>
       </c>
       <c r="E47" s="8" t="n">
         <v>558.51</v>
@@ -4175,7 +4175,7 @@
         <v>22</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>577.02</v>
+        <v>537.14</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>537.14</v>
@@ -4199,7 +4199,7 @@
         <v>65</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>1653.8</v>
+        <v>1575.44</v>
       </c>
       <c r="Q47" s="8" t="n">
         <v>1575.44</v>
@@ -4763,7 +4763,7 @@
         <v>71</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>567.63</v>
+        <v>549.08</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>265.26</v>
@@ -4775,7 +4775,7 @@
         <v>73</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>577.48</v>
+        <v>566.21</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>279.52</v>
@@ -4787,7 +4787,7 @@
         <v>72</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>258.97</v>
+        <v>257.83</v>
       </c>
       <c r="M55" s="8" t="n">
         <v>128.34</v>
@@ -4799,7 +4799,7 @@
         <v>216</v>
       </c>
       <c r="P55" s="8" t="n">
-        <v>1404.09</v>
+        <v>1373.11</v>
       </c>
       <c r="Q55" s="8" t="n">
         <v>673.12</v>
@@ -4990,7 +4990,7 @@
         <v>32</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>429.18</v>
+        <v>426.79</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>429.18</v>
@@ -5002,7 +5002,7 @@
         <v>32</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>437.94</v>
+        <v>435.43</v>
       </c>
       <c r="I58" s="10" t="n">
         <v>437.94</v>
@@ -5014,7 +5014,7 @@
         <v>32</v>
       </c>
       <c r="L58" s="10" t="n">
-        <v>417.77</v>
+        <v>415.33</v>
       </c>
       <c r="M58" s="10" t="n">
         <v>417.77</v>
@@ -5026,7 +5026,7 @@
         <v>96</v>
       </c>
       <c r="P58" s="10" t="n">
-        <v>1284.9</v>
+        <v>1277.55</v>
       </c>
       <c r="Q58" s="10" t="n">
         <v>1284.9</v>
@@ -5213,7 +5213,7 @@
         <v>31</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>383.52</v>
+        <v>369.9</v>
       </c>
       <c r="E61" s="8" t="n">
         <v>178.14</v>
@@ -5225,7 +5225,7 @@
         <v>31</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>414.33</v>
+        <v>404.49</v>
       </c>
       <c r="I61" s="8" t="n">
         <v>197.32</v>
@@ -5237,7 +5237,7 @@
         <v>31</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>446.83</v>
+        <v>437.57</v>
       </c>
       <c r="M61" s="8" t="n">
         <v>214.15</v>
@@ -5249,7 +5249,7 @@
         <v>93</v>
       </c>
       <c r="P61" s="8" t="n">
-        <v>1244.68</v>
+        <v>1211.95</v>
       </c>
       <c r="Q61" s="8" t="n">
         <v>589.61</v>
@@ -5590,7 +5590,7 @@
         <v>38</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>293.27</v>
+        <v>276.16</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>138.08</v>
@@ -5602,7 +5602,7 @@
         <v>39</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>359.71</v>
+        <v>339.58</v>
       </c>
       <c r="I66" s="10" t="n">
         <v>169.79</v>
@@ -5614,7 +5614,7 @@
         <v>39</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>373.65</v>
+        <v>352.63</v>
       </c>
       <c r="M66" s="10" t="n">
         <v>176.31</v>
@@ -5626,7 +5626,7 @@
         <v>116</v>
       </c>
       <c r="P66" s="10" t="n">
-        <v>1026.63</v>
+        <v>968.37</v>
       </c>
       <c r="Q66" s="10" t="n">
         <v>484.18</v>
@@ -5752,7 +5752,7 @@
         <v>21</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>298.94</v>
+        <v>285.54</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>149.47</v>
@@ -5764,7 +5764,7 @@
         <v>21</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>330.04</v>
+        <v>315.11</v>
       </c>
       <c r="I68" s="10" t="n">
         <v>165.02</v>
@@ -5776,7 +5776,7 @@
         <v>21</v>
       </c>
       <c r="L68" s="10" t="n">
-        <v>338.08</v>
+        <v>325.13</v>
       </c>
       <c r="M68" s="10" t="n">
         <v>169.04</v>
@@ -5788,7 +5788,7 @@
         <v>63</v>
       </c>
       <c r="P68" s="10" t="n">
-        <v>967.0700000000001</v>
+        <v>925.78</v>
       </c>
       <c r="Q68" s="10" t="n">
         <v>483.53</v>
@@ -6135,7 +6135,7 @@
         <v>29</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>268.3</v>
+        <v>260.1</v>
       </c>
       <c r="E73" s="8" t="n">
         <v>122.96</v>
@@ -6147,7 +6147,7 @@
         <v>29</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>297.81</v>
+        <v>288.8</v>
       </c>
       <c r="I73" s="8" t="n">
         <v>148.91</v>
@@ -6159,7 +6159,7 @@
         <v>29</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>305.23</v>
+        <v>296.19</v>
       </c>
       <c r="M73" s="8" t="n">
         <v>152.61</v>
@@ -6171,7 +6171,7 @@
         <v>87</v>
       </c>
       <c r="P73" s="8" t="n">
-        <v>871.34</v>
+        <v>845.09</v>
       </c>
       <c r="Q73" s="8" t="n">
         <v>424.48</v>
@@ -6214,7 +6214,7 @@
         <v>31</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>378.94</v>
+        <v>301.43</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>223.93</v>
@@ -6226,7 +6226,7 @@
         <v>31</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>361.56</v>
+        <v>286.77</v>
       </c>
       <c r="I74" s="10" t="n">
         <v>211.99</v>
@@ -6238,7 +6238,7 @@
         <v>30</v>
       </c>
       <c r="L74" s="10" t="n">
-        <v>307.21</v>
+        <v>238.14</v>
       </c>
       <c r="M74" s="10" t="n">
         <v>169.07</v>
@@ -6250,7 +6250,7 @@
         <v>92</v>
       </c>
       <c r="P74" s="10" t="n">
-        <v>1047.7</v>
+        <v>826.34</v>
       </c>
       <c r="Q74" s="10" t="n">
         <v>604.98</v>
@@ -7041,7 +7041,7 @@
         <v>15</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>210.72</v>
+        <v>202.53</v>
       </c>
       <c r="E85" s="8" t="n">
         <v>97.17</v>
@@ -7053,7 +7053,7 @@
         <v>14</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>230.09</v>
+        <v>221.08</v>
       </c>
       <c r="I85" s="8" t="n">
         <v>106.04</v>
@@ -7065,7 +7065,7 @@
         <v>14</v>
       </c>
       <c r="L85" s="8" t="n">
-        <v>234.68</v>
+        <v>225.64</v>
       </c>
       <c r="M85" s="8" t="n">
         <v>108.3</v>
@@ -7077,7 +7077,7 @@
         <v>43</v>
       </c>
       <c r="P85" s="8" t="n">
-        <v>675.5</v>
+        <v>649.26</v>
       </c>
       <c r="Q85" s="8" t="n">
         <v>311.51</v>
@@ -7420,7 +7420,7 @@
         <v>6</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>283.32</v>
+        <v>193.21</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>141.66</v>
@@ -7432,7 +7432,7 @@
         <v>6</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>307.04</v>
+        <v>209.24</v>
       </c>
       <c r="I90" s="10" t="n">
         <v>153.52</v>
@@ -7444,7 +7444,7 @@
         <v>6</v>
       </c>
       <c r="L90" s="10" t="n">
-        <v>288.86</v>
+        <v>186.32</v>
       </c>
       <c r="M90" s="10" t="n">
         <v>144.43</v>
@@ -7456,7 +7456,7 @@
         <v>18</v>
       </c>
       <c r="P90" s="10" t="n">
-        <v>879.22</v>
+        <v>588.77</v>
       </c>
       <c r="Q90" s="10" t="n">
         <v>439.61</v>
@@ -7499,7 +7499,7 @@
         <v>10</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>187.77</v>
+        <v>180.18</v>
       </c>
       <c r="E91" s="8" t="n">
         <v>93.89</v>
@@ -7511,7 +7511,7 @@
         <v>10</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>202.61</v>
+        <v>195.71</v>
       </c>
       <c r="I91" s="8" t="n">
         <v>101.31</v>
@@ -7523,7 +7523,7 @@
         <v>10</v>
       </c>
       <c r="L91" s="8" t="n">
-        <v>213.39</v>
+        <v>207.81</v>
       </c>
       <c r="M91" s="8" t="n">
         <v>106.69</v>
@@ -7535,7 +7535,7 @@
         <v>30</v>
       </c>
       <c r="P91" s="8" t="n">
-        <v>603.77</v>
+        <v>583.7</v>
       </c>
       <c r="Q91" s="8" t="n">
         <v>301.89</v>
@@ -8861,7 +8861,7 @@
         <v>19</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>263.22</v>
+        <v>141.04</v>
       </c>
       <c r="E109" s="8" t="n">
         <v>131.61</v>
@@ -8873,7 +8873,7 @@
         <v>19</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>290.09</v>
+        <v>155.82</v>
       </c>
       <c r="I109" s="8" t="n">
         <v>145.04</v>
@@ -8885,7 +8885,7 @@
         <v>20</v>
       </c>
       <c r="L109" s="8" t="n">
-        <v>311.78</v>
+        <v>166.99</v>
       </c>
       <c r="M109" s="8" t="n">
         <v>155.89</v>
@@ -8897,7 +8897,7 @@
         <v>58</v>
       </c>
       <c r="P109" s="8" t="n">
-        <v>865.09</v>
+        <v>463.85</v>
       </c>
       <c r="Q109" s="8" t="n">
         <v>432.54</v>
@@ -9311,7 +9311,7 @@
         <v>18</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>244.35</v>
+        <v>122.17</v>
       </c>
       <c r="E115" s="8" t="n">
         <v>0</v>
@@ -9323,7 +9323,7 @@
         <v>18</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>268.52</v>
+        <v>134.26</v>
       </c>
       <c r="I115" s="8" t="n">
         <v>0</v>
@@ -9335,7 +9335,7 @@
         <v>18</v>
       </c>
       <c r="L115" s="8" t="n">
-        <v>289.59</v>
+        <v>144.8</v>
       </c>
       <c r="M115" s="8" t="n">
         <v>0</v>
@@ -9347,7 +9347,7 @@
         <v>54</v>
       </c>
       <c r="P115" s="8" t="n">
-        <v>802.46</v>
+        <v>401.23</v>
       </c>
       <c r="Q115" s="8" t="n">
         <v>0</v>
@@ -9927,7 +9927,7 @@
         <v>15</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>111.65</v>
+        <v>108.37</v>
       </c>
       <c r="E123" s="8" t="n">
         <v>55.82</v>
@@ -9939,7 +9939,7 @@
         <v>15</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>122.71</v>
+        <v>119.1</v>
       </c>
       <c r="I123" s="8" t="n">
         <v>61.36</v>
@@ -9951,7 +9951,7 @@
         <v>15</v>
       </c>
       <c r="L123" s="8" t="n">
-        <v>121.95</v>
+        <v>120.73</v>
       </c>
       <c r="M123" s="8" t="n">
         <v>60.98</v>
@@ -9963,7 +9963,7 @@
         <v>45</v>
       </c>
       <c r="P123" s="8" t="n">
-        <v>356.31</v>
+        <v>348.2</v>
       </c>
       <c r="Q123" s="8" t="n">
         <v>178.16</v>
@@ -10624,7 +10624,7 @@
         <v>3</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>114.86</v>
+        <v>110.14</v>
       </c>
       <c r="E132" s="10" t="n">
         <v>114.86</v>
@@ -10636,7 +10636,7 @@
         <v>3</v>
       </c>
       <c r="H132" s="10" t="n">
-        <v>114.5</v>
+        <v>109.68</v>
       </c>
       <c r="I132" s="10" t="n">
         <v>114.5</v>
@@ -10648,7 +10648,7 @@
         <v>3</v>
       </c>
       <c r="L132" s="10" t="n">
-        <v>101.99</v>
+        <v>97.38</v>
       </c>
       <c r="M132" s="10" t="n">
         <v>101.99</v>
@@ -10660,7 +10660,7 @@
         <v>9</v>
       </c>
       <c r="P132" s="10" t="n">
-        <v>331.35</v>
+        <v>317.2</v>
       </c>
       <c r="Q132" s="10" t="n">
         <v>331.35</v>
@@ -10851,7 +10851,7 @@
         <v>15</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>79.97</v>
+        <v>71.88</v>
       </c>
       <c r="E135" s="8" t="n">
         <v>31.9</v>
@@ -10863,7 +10863,7 @@
         <v>18</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>106.01</v>
+        <v>96.72</v>
       </c>
       <c r="I135" s="8" t="n">
         <v>43.71</v>
@@ -10875,7 +10875,7 @@
         <v>19</v>
       </c>
       <c r="L135" s="8" t="n">
-        <v>126.53</v>
+        <v>117.92</v>
       </c>
       <c r="M135" s="8" t="n">
         <v>54.66</v>
@@ -10887,7 +10887,7 @@
         <v>52</v>
       </c>
       <c r="P135" s="8" t="n">
-        <v>312.51</v>
+        <v>286.53</v>
       </c>
       <c r="Q135" s="8" t="n">
         <v>130.27</v>
@@ -12515,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>126.87</v>
+        <v>63.57</v>
       </c>
       <c r="E157" s="8" t="n">
         <v>0.27</v>
@@ -12527,7 +12527,7 @@
         <v>16</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>138.19</v>
+        <v>69.39</v>
       </c>
       <c r="I157" s="8" t="n">
         <v>0.59</v>
@@ -12539,7 +12539,7 @@
         <v>17</v>
       </c>
       <c r="L157" s="8" t="n">
-        <v>137.6</v>
+        <v>68.8</v>
       </c>
       <c r="M157" s="8" t="n">
         <v>0</v>
@@ -12551,7 +12551,7 @@
         <v>49</v>
       </c>
       <c r="P157" s="8" t="n">
-        <v>402.67</v>
+        <v>201.76</v>
       </c>
       <c r="Q157" s="8" t="n">
         <v>0.86</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>126.6</v>
+        <v>63.3</v>
       </c>
       <c r="E158" s="10" t="n">
         <v>126.6</v>
@@ -12600,7 +12600,7 @@
         <v>15</v>
       </c>
       <c r="H158" s="10" t="n">
-        <v>137.61</v>
+        <v>68.8</v>
       </c>
       <c r="I158" s="10" t="n">
         <v>137.61</v>
@@ -12612,7 +12612,7 @@
         <v>17</v>
       </c>
       <c r="L158" s="10" t="n">
-        <v>137.6</v>
+        <v>68.8</v>
       </c>
       <c r="M158" s="10" t="n">
         <v>137.6</v>
@@ -12624,7 +12624,7 @@
         <v>47</v>
       </c>
       <c r="P158" s="10" t="n">
-        <v>401.81</v>
+        <v>200.9</v>
       </c>
       <c r="Q158" s="10" t="n">
         <v>401.81</v>
@@ -14082,7 +14082,7 @@
         <v>10</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>36.72</v>
+        <v>34.15</v>
       </c>
       <c r="E178" s="10" t="n">
         <v>31.59</v>
@@ -14094,7 +14094,7 @@
         <v>10</v>
       </c>
       <c r="H178" s="10" t="n">
-        <v>44.3</v>
+        <v>41.27</v>
       </c>
       <c r="I178" s="10" t="n">
         <v>38.23</v>
@@ -14106,7 +14106,7 @@
         <v>10</v>
       </c>
       <c r="L178" s="10" t="n">
-        <v>49.93</v>
+        <v>46.56</v>
       </c>
       <c r="M178" s="10" t="n">
         <v>43.19</v>
@@ -14118,7 +14118,7 @@
         <v>30</v>
       </c>
       <c r="P178" s="10" t="n">
-        <v>130.96</v>
+        <v>121.98</v>
       </c>
       <c r="Q178" s="10" t="n">
         <v>113.01</v>
@@ -15150,7 +15150,7 @@
         <v>4</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>63.47</v>
+        <v>62.86</v>
       </c>
       <c r="E192" s="10" t="n">
         <v>31.73</v>
@@ -15162,7 +15162,7 @@
         <v>5</v>
       </c>
       <c r="H192" s="10" t="n">
-        <v>14.86</v>
+        <v>13.71</v>
       </c>
       <c r="I192" s="10" t="n">
         <v>7.43</v>
@@ -15174,7 +15174,7 @@
         <v>6</v>
       </c>
       <c r="L192" s="10" t="n">
-        <v>6.1</v>
+        <v>4.6</v>
       </c>
       <c r="M192" s="10" t="n">
         <v>3.05</v>
@@ -15186,7 +15186,7 @@
         <v>15</v>
       </c>
       <c r="P192" s="10" t="n">
-        <v>84.43000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="Q192" s="10" t="n">
         <v>42.22</v>
@@ -16814,7 +16814,7 @@
         <v>3</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>25.99</v>
+        <v>16.5</v>
       </c>
       <c r="E214" s="10" t="n">
         <v>7.01</v>
@@ -16826,7 +16826,7 @@
         <v>3</v>
       </c>
       <c r="H214" s="10" t="n">
-        <v>30.67</v>
+        <v>19.68</v>
       </c>
       <c r="I214" s="10" t="n">
         <v>8.699999999999999</v>
@@ -16838,7 +16838,7 @@
         <v>4</v>
       </c>
       <c r="L214" s="10" t="n">
-        <v>33.48</v>
+        <v>21.85</v>
       </c>
       <c r="M214" s="10" t="n">
         <v>10.22</v>
@@ -16850,7 +16850,7 @@
         <v>10</v>
       </c>
       <c r="P214" s="10" t="n">
-        <v>90.15000000000001</v>
+        <v>58.04</v>
       </c>
       <c r="Q214" s="10" t="n">
         <v>25.93</v>
@@ -17266,7 +17266,7 @@
         <v>3</v>
       </c>
       <c r="H220" s="10" t="n">
-        <v>18.43</v>
+        <v>18.23</v>
       </c>
       <c r="I220" s="10" t="n">
         <v>18.03</v>
@@ -17278,7 +17278,7 @@
         <v>5</v>
       </c>
       <c r="L220" s="10" t="n">
-        <v>16.62</v>
+        <v>15.61</v>
       </c>
       <c r="M220" s="10" t="n">
         <v>14.59</v>
@@ -17290,7 +17290,7 @@
         <v>10</v>
       </c>
       <c r="P220" s="10" t="n">
-        <v>50.2</v>
+        <v>48.98</v>
       </c>
       <c r="Q220" s="10" t="n">
         <v>47.77</v>
@@ -17913,7 +17913,7 @@
         <v>3</v>
       </c>
       <c r="D229" s="8" t="n">
-        <v>28.33</v>
+        <v>14.22</v>
       </c>
       <c r="E229" s="8" t="n">
         <v>0.12</v>
@@ -17925,7 +17925,7 @@
         <v>5</v>
       </c>
       <c r="H229" s="8" t="n">
-        <v>40.07</v>
+        <v>25.58</v>
       </c>
       <c r="I229" s="8" t="n">
         <v>11.1</v>
@@ -17937,7 +17937,7 @@
         <v>7</v>
       </c>
       <c r="L229" s="8" t="n">
-        <v>39.26</v>
+        <v>25.35</v>
       </c>
       <c r="M229" s="8" t="n">
         <v>11.45</v>
@@ -17949,7 +17949,7 @@
         <v>15</v>
       </c>
       <c r="P229" s="8" t="n">
-        <v>107.66</v>
+        <v>65.16</v>
       </c>
       <c r="Q229" s="8" t="n">
         <v>22.66</v>
@@ -18361,7 +18361,7 @@
         <v>2</v>
       </c>
       <c r="D235" s="8" t="n">
-        <v>23.49</v>
+        <v>11.35</v>
       </c>
       <c r="E235" s="8" t="n">
         <v>2.65</v>
@@ -18373,7 +18373,7 @@
         <v>2</v>
       </c>
       <c r="H235" s="8" t="n">
-        <v>27.23</v>
+        <v>13.3</v>
       </c>
       <c r="I235" s="8" t="n">
         <v>3.17</v>
@@ -18385,7 +18385,7 @@
         <v>2</v>
       </c>
       <c r="L235" s="8" t="n">
-        <v>29.04</v>
+        <v>14.37</v>
       </c>
       <c r="M235" s="8" t="n">
         <v>3.52</v>
@@ -18397,7 +18397,7 @@
         <v>6</v>
       </c>
       <c r="P235" s="8" t="n">
-        <v>79.77</v>
+        <v>39.02</v>
       </c>
       <c r="Q235" s="8" t="n">
         <v>9.34</v>
@@ -18981,7 +18981,7 @@
         <v>2</v>
       </c>
       <c r="D243" s="8" t="n">
-        <v>18.98</v>
+        <v>9.49</v>
       </c>
       <c r="E243" s="8" t="n">
         <v>18.98</v>
@@ -18993,7 +18993,7 @@
         <v>2</v>
       </c>
       <c r="H243" s="8" t="n">
-        <v>21.98</v>
+        <v>10.99</v>
       </c>
       <c r="I243" s="8" t="n">
         <v>21.98</v>
@@ -19005,7 +19005,7 @@
         <v>2</v>
       </c>
       <c r="L243" s="8" t="n">
-        <v>23.26</v>
+        <v>11.63</v>
       </c>
       <c r="M243" s="8" t="n">
         <v>23.26</v>
@@ -19017,7 +19017,7 @@
         <v>6</v>
       </c>
       <c r="P243" s="8" t="n">
-        <v>64.22</v>
+        <v>32.11</v>
       </c>
       <c r="Q243" s="8" t="n">
         <v>64.22</v>
@@ -19052,7 +19052,7 @@
         <v>3</v>
       </c>
       <c r="D244" s="10" t="n">
-        <v>21.62</v>
+        <v>10.81</v>
       </c>
       <c r="E244" s="10" t="n">
         <v>10.81</v>
@@ -19064,7 +19064,7 @@
         <v>2</v>
       </c>
       <c r="H244" s="10" t="n">
-        <v>19.16</v>
+        <v>9.58</v>
       </c>
       <c r="I244" s="10" t="n">
         <v>9.58</v>
@@ -19076,7 +19076,7 @@
         <v>2</v>
       </c>
       <c r="L244" s="10" t="n">
-        <v>20.67</v>
+        <v>10.34</v>
       </c>
       <c r="M244" s="10" t="n">
         <v>10.34</v>
@@ -19088,7 +19088,7 @@
         <v>7</v>
       </c>
       <c r="P244" s="10" t="n">
-        <v>61.45</v>
+        <v>30.73</v>
       </c>
       <c r="Q244" s="10" t="n">
         <v>30.73</v>
@@ -19670,7 +19670,7 @@
         <v>3</v>
       </c>
       <c r="D252" s="10" t="n">
-        <v>1.01</v>
+        <v>0.62</v>
       </c>
       <c r="E252" s="10" t="n">
         <v>1.01</v>
@@ -19682,7 +19682,7 @@
         <v>9</v>
       </c>
       <c r="H252" s="10" t="n">
-        <v>9.58</v>
+        <v>6.71</v>
       </c>
       <c r="I252" s="10" t="n">
         <v>9.58</v>
@@ -19694,7 +19694,7 @@
         <v>14</v>
       </c>
       <c r="L252" s="10" t="n">
-        <v>19.18</v>
+        <v>17</v>
       </c>
       <c r="M252" s="10" t="n">
         <v>19.18</v>
@@ -19706,7 +19706,7 @@
         <v>26</v>
       </c>
       <c r="P252" s="10" t="n">
-        <v>29.77</v>
+        <v>24.33</v>
       </c>
       <c r="Q252" s="10" t="n">
         <v>29.77</v>
@@ -20049,7 +20049,7 @@
         <v>3</v>
       </c>
       <c r="D257" s="8" t="n">
-        <v>28.33</v>
+        <v>14.22</v>
       </c>
       <c r="E257" s="8" t="n">
         <v>0.12</v>
@@ -20061,7 +20061,7 @@
         <v>5</v>
       </c>
       <c r="H257" s="8" t="n">
-        <v>40.07</v>
+        <v>25.58</v>
       </c>
       <c r="I257" s="8" t="n">
         <v>11.1</v>
@@ -20073,7 +20073,7 @@
         <v>7</v>
       </c>
       <c r="L257" s="8" t="n">
-        <v>39.26</v>
+        <v>25.35</v>
       </c>
       <c r="M257" s="8" t="n">
         <v>11.45</v>
@@ -20085,7 +20085,7 @@
         <v>15</v>
       </c>
       <c r="P257" s="8" t="n">
-        <v>107.66</v>
+        <v>65.16</v>
       </c>
       <c r="Q257" s="8" t="n">
         <v>22.66</v>
@@ -20347,7 +20347,7 @@
         <v>1</v>
       </c>
       <c r="D261" s="8" t="n">
-        <v>15.18</v>
+        <v>7.59</v>
       </c>
       <c r="E261" s="8" t="n">
         <v>0</v>
@@ -20359,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="H261" s="8" t="n">
-        <v>13.81</v>
+        <v>6.91</v>
       </c>
       <c r="I261" s="8" t="n">
         <v>0</v>
@@ -20371,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="8" t="n">
-        <v>11.16</v>
+        <v>5.58</v>
       </c>
       <c r="M261" s="8" t="n">
         <v>0</v>
@@ -20383,7 +20383,7 @@
         <v>3</v>
       </c>
       <c r="P261" s="8" t="n">
-        <v>40.16</v>
+        <v>20.08</v>
       </c>
       <c r="Q261" s="8" t="n">
         <v>0</v>
@@ -21081,7 +21081,7 @@
         <v>1</v>
       </c>
       <c r="D271" s="8" t="n">
-        <v>12.19</v>
+        <v>6.09</v>
       </c>
       <c r="E271" s="8" t="n">
         <v>0</v>
@@ -21093,7 +21093,7 @@
         <v>1</v>
       </c>
       <c r="H271" s="8" t="n">
-        <v>13.87</v>
+        <v>6.93</v>
       </c>
       <c r="I271" s="8" t="n">
         <v>0</v>
@@ -21105,7 +21105,7 @@
         <v>1</v>
       </c>
       <c r="L271" s="8" t="n">
-        <v>7.48</v>
+        <v>3.74</v>
       </c>
       <c r="M271" s="8" t="n">
         <v>0</v>
@@ -21117,7 +21117,7 @@
         <v>3</v>
       </c>
       <c r="P271" s="8" t="n">
-        <v>33.53</v>
+        <v>16.77</v>
       </c>
       <c r="Q271" s="8" t="n">
         <v>0</v>
@@ -21314,7 +21314,7 @@
         <v>2</v>
       </c>
       <c r="D274" s="10" t="n">
-        <v>6.91</v>
+        <v>4.35</v>
       </c>
       <c r="E274" s="10" t="n">
         <v>6.91</v>
@@ -21326,7 +21326,7 @@
         <v>2</v>
       </c>
       <c r="H274" s="10" t="n">
-        <v>8.18</v>
+        <v>5.14</v>
       </c>
       <c r="I274" s="10" t="n">
         <v>8.18</v>
@@ -21338,7 +21338,7 @@
         <v>2</v>
       </c>
       <c r="L274" s="10" t="n">
-        <v>8.970000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="M274" s="10" t="n">
         <v>8.970000000000001</v>
@@ -21350,7 +21350,7 @@
         <v>6</v>
       </c>
       <c r="P274" s="10" t="n">
-        <v>24.06</v>
+        <v>15.09</v>
       </c>
       <c r="Q274" s="10" t="n">
         <v>24.06</v>
@@ -21529,7 +21529,7 @@
         <v>1</v>
       </c>
       <c r="D277" s="8" t="n">
-        <v>9.16</v>
+        <v>4.58</v>
       </c>
       <c r="E277" s="8" t="n">
         <v>0</v>
@@ -21541,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="H277" s="8" t="n">
-        <v>9.31</v>
+        <v>4.66</v>
       </c>
       <c r="I277" s="8" t="n">
         <v>0</v>
@@ -21553,7 +21553,7 @@
         <v>1</v>
       </c>
       <c r="L277" s="8" t="n">
-        <v>8.83</v>
+        <v>4.42</v>
       </c>
       <c r="M277" s="8" t="n">
         <v>0</v>
@@ -21565,7 +21565,7 @@
         <v>3</v>
       </c>
       <c r="P277" s="8" t="n">
-        <v>27.3</v>
+        <v>13.65</v>
       </c>
       <c r="Q277" s="8" t="n">
         <v>0</v>
@@ -22285,7 +22285,7 @@
         <v>3</v>
       </c>
       <c r="D287" s="8" t="n">
-        <v>1.98</v>
+        <v>0.99</v>
       </c>
       <c r="E287" s="8" t="n">
         <v>0</v>
@@ -22297,7 +22297,7 @@
         <v>3</v>
       </c>
       <c r="H287" s="8" t="n">
-        <v>8.06</v>
+        <v>4.03</v>
       </c>
       <c r="I287" s="8" t="n">
         <v>0</v>
@@ -22309,7 +22309,7 @@
         <v>3</v>
       </c>
       <c r="L287" s="8" t="n">
-        <v>7.35</v>
+        <v>3.68</v>
       </c>
       <c r="M287" s="8" t="n">
         <v>0</v>
@@ -22321,7 +22321,7 @@
         <v>9</v>
       </c>
       <c r="P287" s="8" t="n">
-        <v>17.39</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q287" s="8" t="n">
         <v>0</v>
@@ -23201,7 +23201,7 @@
         <v>1</v>
       </c>
       <c r="D299" s="8" t="n">
-        <v>0.93</v>
+        <v>0.47</v>
       </c>
       <c r="E299" s="8" t="n">
         <v>0.93</v>
@@ -23213,7 +23213,7 @@
         <v>3</v>
       </c>
       <c r="H299" s="8" t="n">
-        <v>2.96</v>
+        <v>1.77</v>
       </c>
       <c r="I299" s="8" t="n">
         <v>2.96</v>
@@ -23225,7 +23225,7 @@
         <v>2</v>
       </c>
       <c r="L299" s="8" t="n">
-        <v>2.52</v>
+        <v>1.65</v>
       </c>
       <c r="M299" s="8" t="n">
         <v>2.52</v>
@@ -23237,7 +23237,7 @@
         <v>6</v>
       </c>
       <c r="P299" s="8" t="n">
-        <v>6.42</v>
+        <v>3.88</v>
       </c>
       <c r="Q299" s="8" t="n">
         <v>6.42</v>
@@ -24350,7 +24350,7 @@
         <v>5050</v>
       </c>
       <c r="D314" s="12" t="n">
-        <v>115612.36</v>
+        <v>107544.78</v>
       </c>
       <c r="E314" s="12" t="n">
         <v>74682.73</v>
@@ -24362,7 +24362,7 @@
         <v>5093</v>
       </c>
       <c r="H314" s="12" t="n">
-        <v>121420.65</v>
+        <v>112760.63</v>
       </c>
       <c r="I314" s="12" t="n">
         <v>77557.31</v>
@@ -24374,7 +24374,7 @@
         <v>5107</v>
       </c>
       <c r="L314" s="12" t="n">
-        <v>115328.96</v>
+        <v>107127.26</v>
       </c>
       <c r="M314" s="12" t="n">
         <v>74048.42999999999</v>
@@ -24386,7 +24386,7 @@
         <v>15250</v>
       </c>
       <c r="P314" s="12" t="n">
-        <v>352362.03</v>
+        <v>327432.69</v>
       </c>
       <c r="Q314" s="12" t="n">
         <v>226288.43</v>

--- a/fee_data_complete_base_20260602_summary.xlsx
+++ b/fee_data_complete_base_20260602_summary.xlsx
@@ -24036,10 +24036,10 @@
         <v>45</v>
       </c>
       <c r="D310" s="10" t="n">
-        <v>0</v>
+        <v>2934.44</v>
       </c>
       <c r="E310" s="10" t="n">
-        <v>0</v>
+        <v>978.15</v>
       </c>
       <c r="F310" s="10" t="n">
         <v>0</v>
@@ -24048,10 +24048,10 @@
         <v>40</v>
       </c>
       <c r="H310" s="10" t="n">
-        <v>0</v>
+        <v>2709.49</v>
       </c>
       <c r="I310" s="10" t="n">
-        <v>0</v>
+        <v>903.16</v>
       </c>
       <c r="J310" s="10" t="n">
         <v>0</v>
@@ -24060,10 +24060,10 @@
         <v>40</v>
       </c>
       <c r="L310" s="10" t="n">
-        <v>0</v>
+        <v>2728.5</v>
       </c>
       <c r="M310" s="10" t="n">
-        <v>0</v>
+        <v>909.5</v>
       </c>
       <c r="N310" s="10" t="n">
         <v>0</v>
@@ -24072,10 +24072,10 @@
         <v>125</v>
       </c>
       <c r="P310" s="10" t="n">
-        <v>0</v>
+        <v>8372.43</v>
       </c>
       <c r="Q310" s="10" t="n">
-        <v>0</v>
+        <v>2790.81</v>
       </c>
       <c r="R310" s="10" t="n">
         <v>0</v>
@@ -24271,10 +24271,10 @@
         <v>7</v>
       </c>
       <c r="D313" s="8" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="E313" s="8" t="n">
-        <v>0</v>
+        <v>122.34</v>
       </c>
       <c r="F313" s="8" t="n">
         <v>0</v>
@@ -24283,10 +24283,10 @@
         <v>7</v>
       </c>
       <c r="H313" s="8" t="n">
-        <v>0</v>
+        <v>399.79</v>
       </c>
       <c r="I313" s="8" t="n">
-        <v>0</v>
+        <v>133.27</v>
       </c>
       <c r="J313" s="8" t="n">
         <v>0</v>
@@ -24295,10 +24295,10 @@
         <v>7</v>
       </c>
       <c r="L313" s="8" t="n">
-        <v>0</v>
+        <v>406.31</v>
       </c>
       <c r="M313" s="8" t="n">
-        <v>0</v>
+        <v>135.44</v>
       </c>
       <c r="N313" s="8" t="n">
         <v>0</v>
@@ -24307,10 +24307,10 @@
         <v>21</v>
       </c>
       <c r="P313" s="8" t="n">
-        <v>0</v>
+        <v>1173.11</v>
       </c>
       <c r="Q313" s="8" t="n">
-        <v>0</v>
+        <v>391.04</v>
       </c>
       <c r="R313" s="8" t="n">
         <v>0</v>
@@ -24350,10 +24350,10 @@
         <v>5050</v>
       </c>
       <c r="D314" s="12" t="n">
-        <v>107544.78</v>
+        <v>110846.22</v>
       </c>
       <c r="E314" s="12" t="n">
-        <v>74682.73</v>
+        <v>75783.22</v>
       </c>
       <c r="F314" s="12" t="n">
         <v>16704.39</v>
@@ -24362,10 +24362,10 @@
         <v>5093</v>
       </c>
       <c r="H314" s="12" t="n">
-        <v>112760.63</v>
+        <v>115869.91</v>
       </c>
       <c r="I314" s="12" t="n">
-        <v>77557.31</v>
+        <v>78593.74000000001</v>
       </c>
       <c r="J314" s="12" t="n">
         <v>17615.24</v>
@@ -24374,10 +24374,10 @@
         <v>5107</v>
       </c>
       <c r="L314" s="12" t="n">
-        <v>107127.26</v>
+        <v>110262.07</v>
       </c>
       <c r="M314" s="12" t="n">
-        <v>74048.42999999999</v>
+        <v>75093.37</v>
       </c>
       <c r="N314" s="12" t="n">
         <v>17261.14</v>
@@ -24386,10 +24386,10 @@
         <v>15250</v>
       </c>
       <c r="P314" s="12" t="n">
-        <v>327432.69</v>
+        <v>336978.23</v>
       </c>
       <c r="Q314" s="12" t="n">
-        <v>226288.43</v>
+        <v>229470.28</v>
       </c>
       <c r="R314" s="12" t="n">
         <v>51580.83</v>
@@ -24469,20 +24469,17 @@
       <c r="E2" s="14" t="n">
         <v>206722.22</v>
       </c>
-      <c r="F2" s="13">
-        <f>'3期サマリー'!D314+'3期サマリー'!E314+'3期サマリー'!F314</f>
-        <v/>
-      </c>
-      <c r="G2" s="26">
-        <f>E2-F2</f>
-        <v/>
+      <c r="F2" s="13" t="n">
+        <v>203319.59</v>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>3402.63</v>
       </c>
       <c r="H2" s="18" t="n">
         <v>3397.43</v>
       </c>
-      <c r="I2" s="26">
-        <f>G2-H2</f>
-        <v/>
+      <c r="I2" s="26" t="n">
+        <v>5.2</v>
       </c>
     </row>
     <row r="3">
@@ -24492,20 +24489,17 @@
       <c r="E3" s="14" t="n">
         <v>215501.73</v>
       </c>
-      <c r="F3" s="13">
-        <f>'3期サマリー'!H314+'3期サマリー'!I314+'3期サマリー'!J314</f>
-        <v/>
-      </c>
-      <c r="G3" s="26">
-        <f>E3-F3</f>
-        <v/>
+      <c r="F3" s="13" t="n">
+        <v>212042.33</v>
+      </c>
+      <c r="G3" s="26" t="n">
+        <v>3459.4</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>3469.98</v>
       </c>
-      <c r="I3" s="26">
-        <f>G3-H3</f>
-        <v/>
+      <c r="I3" s="26" t="n">
+        <v>-10.58</v>
       </c>
     </row>
     <row r="4">
@@ -24515,20 +24509,17 @@
       <c r="E4" s="14" t="n">
         <v>205105.4</v>
       </c>
-      <c r="F4" s="13">
-        <f>'3期サマリー'!L314+'3期サマリー'!M314+'3期サマリー'!N314</f>
-        <v/>
-      </c>
-      <c r="G4" s="26">
-        <f>E4-F4</f>
-        <v/>
+      <c r="F4" s="13" t="n">
+        <v>202579.75</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>2525.65</v>
       </c>
       <c r="H4" s="18" t="n">
         <v>2471.99</v>
       </c>
-      <c r="I4" s="26">
-        <f>G4-H4</f>
-        <v/>
+      <c r="I4" s="26" t="n">
+        <v>53.66</v>
       </c>
     </row>
   </sheetData>
